--- a/outputs/GC-COLLECTION-FULL-VIEW.xlsx
+++ b/outputs/GC-COLLECTION-FULL-VIEW.xlsx
@@ -142,7 +142,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -192,9 +192,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2150,7 +2147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2208,7 +2205,7 @@
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>Buildable (ac)</t>
+          <t>Buildable zone (ac)</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -2264,9 +2261,10 @@
       <c r="F5" s="9" t="n">
         <v>0.2</v>
       </c>
-      <c r="G5" s="29">
-        <f>IF(E5=0,"",(E5-F5)/E5)</f>
-        <v/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>≥65%</t>
+        </is>
       </c>
       <c r="H5" s="28" t="n">
         <v>6</v>
@@ -2288,7 +2286,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="28" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Coffee Fields Forever</t>
         </is>
@@ -2314,11 +2312,12 @@
       <c r="F6" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G6" s="29">
-        <f>IF(E6=0,"",(E6-F6)/E6)</f>
-        <v/>
-      </c>
-      <c r="H6" s="28" t="n">
+      <c r="G6" s="9" t="inlineStr">
+        <is>
+          <t>≥65%</t>
+        </is>
+      </c>
+      <c r="H6" s="9" t="n">
         <v>20</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -2338,7 +2337,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
@@ -2364,11 +2363,12 @@
       <c r="F7" s="9" t="n">
         <v>2.3</v>
       </c>
-      <c r="G7" s="29">
-        <f>IF(E7=0,"",(E7-F7)/E7)</f>
-        <v/>
-      </c>
-      <c r="H7" s="28" t="n">
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>≥65%</t>
+        </is>
+      </c>
+      <c r="H7" s="9" t="n">
         <v>12</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="28" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>The Creek</t>
         </is>
@@ -2414,11 +2414,12 @@
       <c r="F8" s="9" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="29">
-        <f>IF(E8=0,"",(E8-F8)/E8)</f>
-        <v/>
-      </c>
-      <c r="H8" s="28" t="n">
+      <c r="G8" s="9" t="inlineStr">
+        <is>
+          <t>≥65%</t>
+        </is>
+      </c>
+      <c r="H8" s="9" t="n">
         <v>20</v>
       </c>
       <c r="I8" s="9" t="inlineStr">
@@ -2438,7 +2439,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Nine Hills</t>
         </is>
@@ -2464,11 +2465,12 @@
       <c r="F9" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="29">
-        <f>IF(E9=0,"",(E9-F9)/E9)</f>
-        <v/>
-      </c>
-      <c r="H9" s="28" t="n">
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>≥65%</t>
+        </is>
+      </c>
+      <c r="H9" s="9" t="n">
         <v>16</v>
       </c>
       <c r="I9" s="9" t="inlineStr">
@@ -2506,7 +2508,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="29" t="inlineStr">
         <is>
           <t>Solace</t>
         </is>
@@ -2518,7 +2520,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="30" t="inlineStr">
+      <c r="A15" s="29" t="inlineStr">
         <is>
           <t>Solace</t>
         </is>
@@ -2530,7 +2532,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="29" t="inlineStr">
         <is>
           <t>Solace</t>
         </is>
@@ -2541,117 +2543,185 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="30" t="inlineStr">
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Landscape preservation is carried exactly as the ledger states it. It is not recomputed here: the estates build over several levels, so site minus buildable zone is not the landscape figure, and verifying it needs a survey rather than a division.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>KEY TYPOLOGIES</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Estate</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Typology</t>
+        </is>
+      </c>
+      <c r="C21" s="8" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>Sqft each</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr"/>
+      <c r="H21" s="8" t="inlineStr"/>
+      <c r="I21" s="8" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr"/>
+      <c r="K21" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>Solace</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="30" t="n">
+        <v>565</v>
+      </c>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>Grounded, inward-looking courtyard suites. Heavy, shaded, cell-like enclosures.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>Solace</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Sky Canopies</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D23" s="30" t="n">
+        <v>565</v>
+      </c>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="J23" s="9" t="n"/>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>Cantilevered floor plates and a horizon visor canopy that blocks peering from above.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>Solace</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Gabled Twin Pods</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" s="30" t="n">
+        <v>565</v>
+      </c>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>Double-height lounges with private backyard onsens, under 5.5m gabled voids.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>Coffee Fields Forever</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Buildable envelope is 67% of the site, leaving 33% as landscape against a minimum of 65%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="30" t="inlineStr">
-        <is>
-          <t>Confluence</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Buildable envelope is 52% of the site, leaving 48% as landscape against a minimum of 65%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="30" t="inlineStr">
-        <is>
-          <t>The Creek</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Buildable envelope is 50% of the site, leaving 50% as landscape against a minimum of 65%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="30" t="inlineStr">
-        <is>
-          <t>Nine Hills</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Buildable envelope is 40% of the site, leaving 60% as landscape against a minimum of 65%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>The ledger claims ≥65% landscape preservation on every estate. Its own buildable envelopes leave that much on Solace only. Either 'buildable envelope' means the permitted zone rather than the footprint, or four estates are outside the invariant.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>KEY TYPOLOGIES</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>Estate</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>Typology</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>Sqft each</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr"/>
-      <c r="H25" s="8" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr"/>
-      <c r="J25" s="8" t="inlineStr"/>
-      <c r="K25" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Earth (Prithvi)</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>450</v>
+      </c>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="inlineStr">
+        <is>
+          <t>Mivan cast, modular.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="9" t="inlineStr">
         <is>
-          <t>Solace</t>
+          <t>Coffee Fields Forever</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Ether (Akasha)</t>
         </is>
       </c>
       <c r="C26" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D26" s="31" t="n">
-        <v>565</v>
+        <v>6</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>450</v>
       </c>
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="9" t="n"/>
@@ -2661,26 +2731,26 @@
       <c r="J26" s="9" t="n"/>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>Grounded, inward-looking courtyard suites. Heavy, shaded, cell-like enclosures.</t>
+          <t>Mivan cast, modular.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="9" t="inlineStr">
         <is>
-          <t>Solace</t>
+          <t>Coffee Fields Forever</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>Sky Canopies</t>
+          <t>Air (Vayu)</t>
         </is>
       </c>
       <c r="C27" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D27" s="31" t="n">
-        <v>565</v>
+        <v>8</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>450</v>
       </c>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
@@ -2690,26 +2760,26 @@
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="inlineStr">
         <is>
-          <t>Cantilevered floor plates and a horizon visor canopy that blocks peering from above.</t>
+          <t>Mivan cast, modular.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="9" t="inlineStr">
         <is>
-          <t>Solace</t>
+          <t>Coffee Fields Forever</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
         <is>
-          <t>Gabled Twin Pods</t>
+          <t>Tree House</t>
         </is>
       </c>
       <c r="C28" s="26" t="n">
-        <v>2</v>
-      </c>
-      <c r="D28" s="31" t="n">
-        <v>565</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>322</v>
       </c>
       <c r="E28" s="9" t="n"/>
       <c r="F28" s="9" t="n"/>
@@ -2719,26 +2789,26 @@
       <c r="J28" s="9" t="n"/>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>Double-height lounges with private backyard onsens, under 5.5m gabled voids.</t>
+          <t>Tension-suspended stilt cabin in the canopy. Not Mivan.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="9" t="inlineStr">
         <is>
-          <t>Coffee Fields Forever</t>
+          <t>Confluence</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
         <is>
-          <t>Earth (Prithvi)</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="C29" s="26" t="n">
         <v>6</v>
       </c>
       <c r="D29" s="26" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="9" t="n"/>
@@ -2748,26 +2818,26 @@
       <c r="J29" s="9" t="n"/>
       <c r="K29" s="9" t="inlineStr">
         <is>
-          <t>Mivan cast, modular.</t>
+          <t>Grounded, shaded, inward-looking cells opening to private courtyards.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="9" t="inlineStr">
         <is>
-          <t>Coffee Fields Forever</t>
+          <t>Confluence</t>
         </is>
       </c>
       <c r="B30" s="9" t="inlineStr">
         <is>
-          <t>Ether (Akasha)</t>
+          <t>Sky</t>
         </is>
       </c>
       <c r="C30" s="26" t="n">
         <v>6</v>
       </c>
       <c r="D30" s="26" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="E30" s="9" t="n"/>
       <c r="F30" s="9" t="n"/>
@@ -2777,113 +2847,68 @@
       <c r="J30" s="9" t="n"/>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>Mivan cast, modular.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Coffee Fields Forever</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Air (Vayu)</t>
-        </is>
-      </c>
-      <c r="C31" s="26" t="n">
-        <v>8</v>
-      </c>
-      <c r="D31" s="26" t="n">
-        <v>450</v>
-      </c>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="9" t="n"/>
-      <c r="G31" s="9" t="n"/>
-      <c r="H31" s="9" t="n"/>
-      <c r="I31" s="9" t="n"/>
-      <c r="J31" s="9" t="n"/>
-      <c r="K31" s="9" t="inlineStr">
-        <is>
-          <t>Mivan cast, modular.</t>
+          <t>Post-tensioned cantilevered view-visor decks.</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
-        <is>
-          <t>Coffee Fields Forever</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="inlineStr">
-        <is>
-          <t>Tree House</t>
-        </is>
-      </c>
-      <c r="C32" s="26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="26" t="n">
-        <v>322</v>
-      </c>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="9" t="n"/>
-      <c r="G32" s="9" t="n"/>
-      <c r="H32" s="9" t="n"/>
-      <c r="I32" s="9" t="n"/>
-      <c r="J32" s="9" t="n"/>
-      <c r="K32" s="9" t="inlineStr">
-        <is>
-          <t>Tension-suspended stilt cabin in the canopy. Not Mivan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="9" t="inlineStr">
-        <is>
-          <t>Confluence</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="inlineStr">
-        <is>
-          <t>Earth</t>
-        </is>
-      </c>
-      <c r="C33" s="26" t="n">
-        <v>6</v>
-      </c>
-      <c r="D33" s="26" t="n">
-        <v>500</v>
-      </c>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="inlineStr">
-        <is>
-          <t>Grounded, shaded, inward-looking cells opening to private courtyards.</t>
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>FOOTPRINT (sqft)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Estate</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Lodging built</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>Working built</t>
+        </is>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Hardscape</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Softscape</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr"/>
+      <c r="H33" s="8" t="inlineStr"/>
+      <c r="I33" s="8" t="inlineStr"/>
+      <c r="J33" s="8" t="inlineStr"/>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Note</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="9" t="inlineStr">
         <is>
-          <t>Confluence</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="inlineStr">
-        <is>
-          <t>Sky</t>
-        </is>
+          <t>Solace</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n">
+        <v>5020</v>
       </c>
       <c r="C34" s="26" t="n">
-        <v>6</v>
+        <v>2992</v>
       </c>
       <c r="D34" s="26" t="n">
-        <v>500</v>
+        <v>6942</v>
       </c>
       <c r="E34" s="9" t="n"/>
       <c r="F34" s="9" t="n"/>
@@ -2893,141 +2918,118 @@
       <c r="J34" s="9" t="n"/>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>Post-tensioned cantilevered view-visor decks.</t>
+          <t>The working half is meant to be invisible; a single built-area figure would hide whether that held.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>Coffee Fields Forever</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n">
+        <v>11372</v>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>3760</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>7905</v>
+      </c>
+      <c r="E35" s="26" t="n">
+        <v>4800</v>
+      </c>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="J35" s="9" t="n"/>
+      <c r="K35" s="9" t="inlineStr">
+        <is>
+          <t>The working half is meant to be invisible; a single built-area figure would hide whether that held.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>FOOTPRINT (sqft)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Estate</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
-        <is>
-          <t>Lodging built</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>Working built</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="inlineStr">
-        <is>
-          <t>Hardscape</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>Softscape</t>
-        </is>
-      </c>
-      <c r="F37" s="8" t="inlineStr"/>
-      <c r="G37" s="8" t="inlineStr"/>
-      <c r="H37" s="8" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr"/>
-      <c r="J37" s="8" t="inlineStr"/>
-      <c r="K37" s="8" t="inlineStr">
-        <is>
-          <t>Note</t>
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Confluence</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n">
+        <v>7700</v>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>3300</v>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>8617</v>
+      </c>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="J36" s="9" t="n"/>
+      <c r="K36" s="9" t="inlineStr">
+        <is>
+          <t>The working half is meant to be invisible; a single built-area figure would hide whether that held.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
-        <is>
-          <t>Solace</t>
-        </is>
-      </c>
-      <c r="B38" s="26" t="n">
-        <v>5020</v>
-      </c>
-      <c r="C38" s="26" t="n">
-        <v>2992</v>
-      </c>
-      <c r="D38" s="26" t="n">
-        <v>6942</v>
-      </c>
-      <c r="E38" s="9" t="n"/>
-      <c r="F38" s="9" t="n"/>
-      <c r="G38" s="9" t="n"/>
-      <c r="H38" s="9" t="n"/>
-      <c r="I38" s="9" t="n"/>
-      <c r="J38" s="9" t="n"/>
-      <c r="K38" s="9" t="inlineStr">
-        <is>
-          <t>The working half is meant to be invisible; a single built-area figure would hide whether that held.</t>
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>ARCHITECTURAL LANGUAGE — common to every climate pack</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
-        <is>
-          <t>Coffee Fields Forever</t>
-        </is>
-      </c>
-      <c r="B39" s="26" t="n">
-        <v>11372</v>
-      </c>
-      <c r="C39" s="26" t="n">
-        <v>3760</v>
-      </c>
-      <c r="D39" s="26" t="n">
-        <v>7905</v>
-      </c>
-      <c r="E39" s="26" t="n">
-        <v>4800</v>
-      </c>
-      <c r="F39" s="9" t="n"/>
-      <c r="G39" s="9" t="n"/>
-      <c r="H39" s="9" t="n"/>
-      <c r="I39" s="9" t="n"/>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="inlineStr">
-        <is>
-          <t>The working half is meant to be invisible; a single built-area figure would hide whether that held.</t>
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Floating horizontal canopy architecture</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="9" t="inlineStr">
-        <is>
-          <t>Confluence</t>
-        </is>
-      </c>
-      <c r="B40" s="26" t="n">
-        <v>7700</v>
-      </c>
-      <c r="C40" s="26" t="n">
-        <v>3300</v>
-      </c>
-      <c r="D40" s="26" t="n">
-        <v>8617</v>
-      </c>
-      <c r="E40" s="9" t="n"/>
-      <c r="F40" s="9" t="n"/>
-      <c r="G40" s="9" t="n"/>
-      <c r="H40" s="9" t="n"/>
-      <c r="I40" s="9" t="n"/>
-      <c r="J40" s="9" t="n"/>
-      <c r="K40" s="9" t="inlineStr">
-        <is>
-          <t>The working half is meant to be invisible; a single built-area figure would hide whether that held.</t>
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Deep protective overhangs</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Key-first planning</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>ARCHITECTURAL LANGUAGE — common to every climate pack</t>
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>·</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Native ecological restoration</t>
         </is>
       </c>
     </row>
@@ -3039,7 +3041,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Floating horizontal canopy architecture</t>
+          <t>Passive environmental performance</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3053,7 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Deep protective overhangs</t>
+          <t>Minimal and tactile material palettes</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3065,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Key-first planning</t>
+          <t>Framed landscape views</t>
         </is>
       </c>
     </row>
@@ -3075,161 +3077,109 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Native ecological restoration</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Passive environmental performance</t>
+          <t>Invisible operational infrastructure</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Minimal and tactile material palettes</t>
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>PLATFORM FINANCIAL CONSTITUTION</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Framed landscape views</t>
+          <t>Maximum standard key size</t>
+        </is>
+      </c>
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>550 sqft</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>·</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Invisible operational infrastructure</t>
+          <t>Maximum key development cost</t>
+        </is>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>₹50 lakh</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>Commons investment envelope</t>
+        </is>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>₹1.0 Cr – ₹3.5 Cr</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>PLATFORM FINANCIAL CONSTITUTION</t>
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>Minimum landscape preservation</t>
+        </is>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>65% of site area</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Maximum standard key size</t>
-        </is>
-      </c>
-      <c r="B53" s="32" t="inlineStr">
-        <is>
-          <t>550 sqft</t>
+          <t>Revenue priority</t>
+        </is>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>Keys before anything built beside them</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Maximum key development cost</t>
-        </is>
-      </c>
-      <c r="B54" s="32" t="inlineStr">
-        <is>
-          <t>₹50 lakh</t>
+          <t>Design reuse target</t>
+        </is>
+      </c>
+      <c r="B54" s="31" t="inlineStr">
+        <is>
+          <t>Above 90%</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Commons investment envelope</t>
-        </is>
-      </c>
-      <c r="B55" s="32" t="inlineStr">
-        <is>
-          <t>₹1.0 Cr – ₹3.5 Cr</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="7" t="inlineStr">
-        <is>
-          <t>Minimum landscape preservation</t>
-        </is>
-      </c>
-      <c r="B56" s="32" t="inlineStr">
-        <is>
-          <t>65% of site area</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="7" t="inlineStr">
-        <is>
-          <t>Revenue priority</t>
-        </is>
-      </c>
-      <c r="B57" s="32" t="inlineStr">
-        <is>
-          <t>Keys before anything built beside them</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>Design reuse target</t>
-        </is>
-      </c>
-      <c r="B58" s="32" t="inlineStr">
-        <is>
-          <t>Above 90%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
           <t>Component standardisation</t>
         </is>
       </c>
-      <c r="B59" s="32" t="inlineStr">
+      <c r="B55" s="31" t="inlineStr">
         <is>
           <t>Above 95%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A22:K22"/>
+  <mergeCells count="6">
+    <mergeCell ref="A18:K18"/>
     <mergeCell ref="B14:K14"/>
-    <mergeCell ref="B17:K17"/>
-    <mergeCell ref="B18:K18"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="B15:K15"/>
     <mergeCell ref="B16:K16"/>
-    <mergeCell ref="B20:K20"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B19:K19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3299,292 +3249,292 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="33" t="inlineStr">
+      <c r="A5" s="32" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="B5" s="33" t="inlineStr">
+      <c r="B5" s="32" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t>Form the LLP, establish authority and assemble the formation record.</t>
         </is>
       </c>
-      <c r="D5" s="33" t="inlineStr">
+      <c r="D5" s="32" t="inlineStr">
         <is>
           <t>VEHICLE READY</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="32" t="inlineStr">
         <is>
           <t>Legal / Control Office</t>
         </is>
       </c>
-      <c r="F5" s="33" t="inlineStr">
+      <c r="F5" s="32" t="inlineStr">
         <is>
           <t>slowspace, solace</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="33" t="inlineStr">
+      <c r="A6" s="32" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="32" t="inlineStr">
         <is>
           <t>Offer</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="32" t="inlineStr">
         <is>
           <t>Approve the proposition, capacity, evidence, risk and access controls.</t>
         </is>
       </c>
-      <c r="D6" s="33" t="inlineStr">
+      <c r="D6" s="32" t="inlineStr">
         <is>
           <t>OFFER OPEN</t>
         </is>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="32" t="inlineStr">
         <is>
           <t>IR / Compliance</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="32" t="inlineStr">
         <is>
           <t>coorgcreek</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="34" t="inlineStr">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>03</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="33" t="inlineStr">
         <is>
           <t>Partners &amp; KYC</t>
         </is>
       </c>
-      <c r="C7" s="34" t="inlineStr">
+      <c r="C7" s="33" t="inlineStr">
         <is>
           <t>Qualify each prospective Partner and preserve the identity evidence.</t>
         </is>
       </c>
-      <c r="D7" s="34" t="inlineStr">
+      <c r="D7" s="33" t="inlineStr">
         <is>
           <t>PARTNER CLEARED</t>
         </is>
       </c>
-      <c r="E7" s="34" t="inlineStr">
+      <c r="E7" s="33" t="inlineStr">
         <is>
           <t>IR / Compliance</t>
         </is>
       </c>
-      <c r="F7" s="34" t="inlineStr"/>
+      <c r="F7" s="33" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="34" t="inlineStr">
+      <c r="A8" s="33" t="inlineStr">
         <is>
           <t>04</t>
         </is>
       </c>
-      <c r="B8" s="34" t="inlineStr">
+      <c r="B8" s="33" t="inlineStr">
         <is>
           <t>Settlement</t>
         </is>
       </c>
-      <c r="C8" s="34" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t>Verify funds, reconcile the transaction and complete controlled settlement.</t>
         </is>
       </c>
-      <c r="D8" s="34" t="inlineStr">
+      <c r="D8" s="33" t="inlineStr">
         <is>
           <t>FUNDS SETTLED</t>
         </is>
       </c>
-      <c r="E8" s="34" t="inlineStr">
+      <c r="E8" s="33" t="inlineStr">
         <is>
           <t>Finance / Legal</t>
         </is>
       </c>
-      <c r="F8" s="34" t="inlineStr"/>
+      <c r="F8" s="33" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="34" t="inlineStr">
+      <c r="A9" s="33" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="B9" s="34" t="inlineStr">
+      <c r="B9" s="33" t="inlineStr">
         <is>
           <t>Ownership</t>
         </is>
       </c>
-      <c r="C9" s="34" t="inlineStr">
+      <c r="C9" s="33" t="inlineStr">
         <is>
           <t>Admit the Partner, issue the interest and update the constitutional registers.</t>
         </is>
       </c>
-      <c r="D9" s="34" t="inlineStr">
+      <c r="D9" s="33" t="inlineStr">
         <is>
           <t>INTEREST ISSUED</t>
         </is>
       </c>
-      <c r="E9" s="34" t="inlineStr">
+      <c r="E9" s="33" t="inlineStr">
         <is>
           <t>Legal / Finance</t>
         </is>
       </c>
-      <c r="F9" s="34" t="inlineStr"/>
+      <c r="F9" s="33" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="34" t="inlineStr">
+      <c r="A10" s="33" t="inlineStr">
         <is>
           <t>06</t>
         </is>
       </c>
-      <c r="B10" s="34" t="inlineStr">
+      <c r="B10" s="33" t="inlineStr">
         <is>
           <t>Governance</t>
         </is>
       </c>
-      <c r="C10" s="34" t="inlineStr">
+      <c r="C10" s="33" t="inlineStr">
         <is>
           <t>Activate rights, policies, authorities, resolutions and compliance controls.</t>
         </is>
       </c>
-      <c r="D10" s="34" t="inlineStr">
+      <c r="D10" s="33" t="inlineStr">
         <is>
           <t>AUTHORITY CURRENT</t>
         </is>
       </c>
-      <c r="E10" s="34" t="inlineStr">
+      <c r="E10" s="33" t="inlineStr">
         <is>
           <t>Board / Governance</t>
         </is>
       </c>
-      <c r="F10" s="34" t="inlineStr"/>
+      <c r="F10" s="33" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="34" t="inlineStr">
+      <c r="A11" s="33" t="inlineStr">
         <is>
           <t>07</t>
         </is>
       </c>
-      <c r="B11" s="34" t="inlineStr">
+      <c r="B11" s="33" t="inlineStr">
         <is>
           <t>Space + Progress</t>
         </is>
       </c>
-      <c r="C11" s="34" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t>Control the asset, baseline, budget, delivery evidence and material change.</t>
         </is>
       </c>
-      <c r="D11" s="34" t="inlineStr">
+      <c r="D11" s="33" t="inlineStr">
         <is>
           <t>DELIVERY CONTROLLED</t>
         </is>
       </c>
-      <c r="E11" s="34" t="inlineStr">
+      <c r="E11" s="33" t="inlineStr">
         <is>
           <t>COO / Project</t>
         </is>
       </c>
-      <c r="F11" s="34" t="inlineStr"/>
+      <c r="F11" s="33" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="34" t="inlineStr">
+      <c r="A12" s="33" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="33" t="inlineStr">
         <is>
           <t>Live + Time</t>
         </is>
       </c>
-      <c r="C12" s="34" t="inlineStr">
+      <c r="C12" s="33" t="inlineStr">
         <is>
           <t>Publish the annual pool, derive entitlements and hand allocation to operations.</t>
         </is>
       </c>
-      <c r="D12" s="34" t="inlineStr">
+      <c r="D12" s="33" t="inlineStr">
         <is>
           <t>TIME PUBLISHED</t>
         </is>
       </c>
-      <c r="E12" s="34" t="inlineStr">
+      <c r="E12" s="33" t="inlineStr">
         <is>
           <t>Time Office / Operations</t>
         </is>
       </c>
-      <c r="F12" s="34" t="inlineStr"/>
+      <c r="F12" s="33" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="34" t="inlineStr">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B13" s="34" t="inlineStr">
+      <c r="B13" s="33" t="inlineStr">
         <is>
           <t>Cashflow + Value</t>
         </is>
       </c>
-      <c r="C13" s="34" t="inlineStr">
+      <c r="C13" s="33" t="inlineStr">
         <is>
           <t>Close periods, preserve reserves, value the interest and execute distributions.</t>
         </is>
       </c>
-      <c r="D13" s="34" t="inlineStr">
+      <c r="D13" s="33" t="inlineStr">
         <is>
           <t>PERIOD CLOSED</t>
         </is>
       </c>
-      <c r="E13" s="34" t="inlineStr">
+      <c r="E13" s="33" t="inlineStr">
         <is>
           <t>Finance / Board</t>
         </is>
       </c>
-      <c r="F13" s="34" t="inlineStr"/>
+      <c r="F13" s="33" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="34" t="inlineStr">
+      <c r="A14" s="33" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B14" s="34" t="inlineStr">
+      <c r="B14" s="33" t="inlineStr">
         <is>
           <t>Board + Comms</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="33" t="inlineStr">
         <is>
           <t>Prepare meetings, decide matters, issue notices and preserve the board record.</t>
         </is>
       </c>
-      <c r="D14" s="34" t="inlineStr">
+      <c r="D14" s="33" t="inlineStr">
         <is>
           <t>BOARD RECORD CURRENT</t>
         </is>
       </c>
-      <c r="E14" s="34" t="inlineStr">
+      <c r="E14" s="33" t="inlineStr">
         <is>
           <t>Board / Communications</t>
         </is>
       </c>
-      <c r="F14" s="34" t="inlineStr"/>
+      <c r="F14" s="33" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -3856,80 +3806,80 @@
       </c>
     </row>
     <row r="5" ht="84" customHeight="1">
-      <c r="A5" s="35" t="inlineStr">
+      <c r="A5" s="34" t="inlineStr">
         <is>
           <t>C-01</t>
         </is>
       </c>
-      <c r="B5" s="35" t="inlineStr">
+      <c r="B5" s="34" t="inlineStr">
         <is>
           <t>solace</t>
         </is>
       </c>
-      <c r="C5" s="36" t="inlineStr">
+      <c r="C5" s="35" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="D5" s="35" t="inlineStr">
+      <c r="D5" s="34" t="inlineStr">
         <is>
           <t>Site area disagrees with the portfolio registry.</t>
         </is>
       </c>
-      <c r="E5" s="35" t="inlineStr">
+      <c r="E5" s="34" t="inlineStr">
         <is>
           <t>• Intake sheet 2: 1.55 acres (0.20 owned + 1.35 leased)
 • Spatial ledger: site area 0.6 acres, buildable envelope 0.2 acres
 The ledger narrows this rather than settling it. Its 0.2-acre buildable envelope matches the intake's 0.20 owned exactly, which suggests the registry measures the owned parcel and the intake measures owned plus leased. That is a reading, not a confirmation, and the difference decides what a partner is told they have a share of.</t>
         </is>
       </c>
-      <c r="F5" s="35" t="inlineStr">
+      <c r="F5" s="34" t="inlineStr">
         <is>
           <t>Confirmation that 0.6 acres is the owned parcel and 1.55 includes the lease</t>
         </is>
       </c>
     </row>
     <row r="6" ht="84" customHeight="1">
-      <c r="A6" s="35" t="inlineStr">
+      <c r="A6" s="34" t="inlineStr">
         <is>
           <t>C-02</t>
         </is>
       </c>
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="34" t="inlineStr">
         <is>
           <t>coorgcreek</t>
         </is>
       </c>
-      <c r="C6" s="36" t="inlineStr">
+      <c r="C6" s="35" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="34" t="inlineStr">
         <is>
           <t>The vehicle is The Creek. Its name says otherwise. — SETTLED 4 Aug 2026</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="34" t="inlineStr">
         <is>
           <t>• Intake: Coorg Coffee Creek LLP, 10 acres, 20 keys
 • Spatial ledger: The Creek, Coorg, 10.0 acres, 5.0 buildable, 20 keys
 Founder confirmed the Coorg vehicle is The Creek, which the matching area and key count had already suggested. What remains is only the name: 'Coorg Coffee Creek' borrows its middle word from Coffee Fields Forever, a different estate three acres in size, and a reader searching either name should not land on the wrong ground. Kept as advisory so the naming is fixed deliberately rather than forgotten.</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="34" t="inlineStr">
         <is>
           <t>Settled. The registered name is the remaining tidy-up.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="84" customHeight="1">
-      <c r="A7" s="37" t="inlineStr">
+      <c r="A7" s="36" t="inlineStr">
         <is>
           <t>C-03</t>
         </is>
       </c>
-      <c r="B7" s="37" t="inlineStr">
+      <c r="B7" s="36" t="inlineStr">
         <is>
           <t>solace</t>
         </is>
@@ -3939,31 +3889,31 @@
           <t>BLOCKING</t>
         </is>
       </c>
-      <c r="D7" s="37" t="inlineStr">
+      <c r="D7" s="36" t="inlineStr">
         <is>
           <t>The capital stack disagrees with the offering sheet.</t>
         </is>
       </c>
-      <c r="E7" s="37" t="inlineStr">
+      <c r="E7" s="36" t="inlineStr">
         <is>
           <t>• Sheet 3 (Capital stack): equity ₹2.00 Cr, project ₹5.00 Cr
 • Sheet 4 (Units &amp; ladder): equity ₹2.50 Cr, project ₹5.50 Cr
 ₹50 lakh of equity, and the two sheets are the two places the same number is stated. Every unit price, share percentage and yield for this vehicle divides by it.</t>
         </is>
       </c>
-      <c r="F7" s="37" t="inlineStr">
+      <c r="F7" s="36" t="inlineStr">
         <is>
           <t>Whichever sheet is current</t>
         </is>
       </c>
     </row>
     <row r="8" ht="84" customHeight="1">
-      <c r="A8" s="37" t="inlineStr">
+      <c r="A8" s="36" t="inlineStr">
         <is>
           <t>C-04</t>
         </is>
       </c>
-      <c r="B8" s="37" t="inlineStr">
+      <c r="B8" s="36" t="inlineStr">
         <is>
           <t>slowspace</t>
         </is>
@@ -3973,12 +3923,12 @@
           <t>BLOCKING</t>
         </is>
       </c>
-      <c r="D8" s="37" t="inlineStr">
+      <c r="D8" s="36" t="inlineStr">
         <is>
           <t>Site area disagrees with the figure the platform has been showing.</t>
         </is>
       </c>
-      <c r="E8" s="37" t="inlineStr">
+      <c r="E8" s="36" t="inlineStr">
         <is>
           <t>• Intake sheet 2: .3 acres · dual frontage
 • app/_assemblies/data.ts, from the site dossier: 1.42 acres · dual frontage
@@ -3986,19 +3936,19 @@
 Three figures for one site, on the vehicle that is already public and already has five of six units subscribed. The ledger's 2.3-acre buildable envelope is close enough to the intake's '.3' to suggest a truncated 2.3 — which would make the site 4.4 acres and both smaller figures wrong. Somebody who has committed money has been shown one of these.</t>
         </is>
       </c>
-      <c r="F8" s="37" t="inlineStr">
+      <c r="F8" s="36" t="inlineStr">
         <is>
           <t>The survey record, against the Confluence site dossier</t>
         </is>
       </c>
     </row>
     <row r="9" ht="84" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="36" t="inlineStr">
         <is>
           <t>C-05</t>
         </is>
       </c>
-      <c r="B9" s="37" t="inlineStr">
+      <c r="B9" s="36" t="inlineStr">
         <is>
           <t>solace</t>
         </is>
@@ -4008,31 +3958,31 @@
           <t>BLOCKING</t>
         </is>
       </c>
-      <c r="D9" s="37" t="inlineStr">
+      <c r="D9" s="36" t="inlineStr">
         <is>
           <t>The waterfall is not stated.</t>
         </is>
       </c>
-      <c r="E9" s="37" t="inlineStr">
+      <c r="E9" s="36" t="inlineStr">
         <is>
           <t>• Sheet 5: five of six stages blank, with 10000 bps against 'to partners'
 • Every other vehicle: six stages summing to 10000 bps
 Read literally it gives partners 100% of gross with no operator share, no reserve, no sinking fund and no debt service, on a vehicle carrying a ₹3.0 Cr facility. It is a blank row rather than a split, so nothing is transcribed.</t>
         </is>
       </c>
-      <c r="F9" s="37" t="inlineStr">
+      <c r="F9" s="36" t="inlineStr">
         <is>
           <t>The six-stage split for this vehicle</t>
         </is>
       </c>
     </row>
     <row r="10" ht="84" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+      <c r="A10" s="36" t="inlineStr">
         <is>
           <t>C-06</t>
         </is>
       </c>
-      <c r="B10" s="37" t="inlineStr">
+      <c r="B10" s="36" t="inlineStr">
         <is>
           <t>slowspace</t>
         </is>
@@ -4042,99 +3992,99 @@
           <t>BLOCKING</t>
         </is>
       </c>
-      <c r="D10" s="37" t="inlineStr">
+      <c r="D10" s="36" t="inlineStr">
         <is>
           <t>The unit structure disagrees with the modelled canon.</t>
         </is>
       </c>
-      <c r="E10" s="37" t="inlineStr">
+      <c r="E10" s="36" t="inlineStr">
         <is>
           <t>• Intake sheet 4: 6 units at ₹40,00,000, 5 subscribed, 1 available, plus a ₹1.6 Cr promoter stake
 • app/_assemblies/slowspace.ts: 20 units at ₹20,00,000, 11 subscribed, 45% remaining, no promoter
 These are different instruments, not different roundings. The intake introduces a 40% sponsor stake the canon does not model, and moves availability from 45% to 10%. The public offering page currently reads from the canon.</t>
         </is>
       </c>
-      <c r="F10" s="37" t="inlineStr">
+      <c r="F10" s="36" t="inlineStr">
         <is>
           <t>Whether the promoter stake is real, and which availability is current</t>
         </is>
       </c>
     </row>
     <row r="11" ht="84" customHeight="1">
-      <c r="A11" s="35" t="inlineStr">
+      <c r="A11" s="34" t="inlineStr">
         <is>
           <t>C-07</t>
         </is>
       </c>
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="34" t="inlineStr">
         <is>
           <t>coorgcreek</t>
         </is>
       </c>
-      <c r="C11" s="36" t="inlineStr">
+      <c r="C11" s="35" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="34" t="inlineStr">
         <is>
           <t>The brand disagrees.</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="34" t="inlineStr">
         <is>
           <t>• Intake sheet 2: SlowSpace brand
 • Spatial ledger: The Creek is ESKAPE
 Both Coorg estates in the ledger are ESKAPE and the intake puts this one under SlowSpace. The brand decides which design pack, which price position and which name a partner is buying into, so it is not a labelling detail.</t>
         </is>
       </c>
-      <c r="F11" s="35" t="inlineStr">
+      <c r="F11" s="34" t="inlineStr">
         <is>
           <t>Which brand The Creek is being developed under</t>
         </is>
       </c>
     </row>
     <row r="12" ht="84" customHeight="1">
-      <c r="A12" s="35" t="inlineStr">
+      <c r="A12" s="34" t="inlineStr">
         <is>
           <t>C-08</t>
         </is>
       </c>
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>solace</t>
         </is>
       </c>
-      <c r="C12" s="36" t="inlineStr">
+      <c r="C12" s="35" t="inlineStr">
         <is>
           <t>ADVISORY</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="34" t="inlineStr">
         <is>
           <t>The studios exceed the platform's own maximum.</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="34" t="inlineStr">
         <is>
           <t>• Spatial ledger, SOLACE sheet: keys at 565 sqft
 • Platform financial constitution: maximum standard key size 550 sqft
 Fifteen square feet, and the standard is stated in the same document. Either Solace is a declared exception or the maximum has moved; leaving it unstated makes the constitution decorative. constants/spatial.ts reports it on every render.</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="34" t="inlineStr">
         <is>
           <t>Whether Solace is an exception or the standard is now 565</t>
         </is>
       </c>
     </row>
     <row r="13" ht="84" customHeight="1">
-      <c r="A13" s="37" t="inlineStr">
+      <c r="A13" s="36" t="inlineStr">
         <is>
           <t>C-09</t>
         </is>
       </c>
-      <c r="B13" s="37" t="inlineStr">
+      <c r="B13" s="36" t="inlineStr">
         <is>
           <t>slowspace</t>
         </is>
@@ -4144,19 +4094,19 @@
           <t>BLOCKING</t>
         </is>
       </c>
-      <c r="D13" s="37" t="inlineStr">
+      <c r="D13" s="36" t="inlineStr">
         <is>
           <t>Entitlement begins five months after construction ends.</t>
         </is>
       </c>
-      <c r="E13" s="37" t="inlineStr">
+      <c r="E13" s="36" t="inlineStr">
         <is>
           <t>• Intake sheet 6: entitlement begins at handover, Jan 2028
 • Spatial ledger gantt: Confluence runs Sep 2026 – Aug 2027
 A partner subscribing today is told when they can first use the place. The two documents disagree by five months, and the earlier date is the one in the construction programme while the later one is in the document a partner reads.</t>
         </is>
       </c>
-      <c r="F13" s="37" t="inlineStr">
+      <c r="F13" s="36" t="inlineStr">
         <is>
           <t>The programme date, against what subscribers have been told</t>
         </is>
